--- a/reports/集团总公司_现金流量表_2025-09.xlsx
+++ b/reports/集团总公司_现金流量表_2025-09.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>204750000</v>
+        <v>203741023</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1776450000</v>
+        <v>1775392325</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4230457</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>36555035</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2095492</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>18243189</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1056065</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>9140888</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>840133</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>7297186</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>631817</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>5483379</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>421400</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>3650093</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>314923</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>2740133</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>211279</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>1826261</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>523773</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>4563724</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>265772</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2296023</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>166500</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1450252</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>556500</v>
+        <v>558819</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>4828300</v>
+        <v>4833408</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3780000</v>
+        <v>3768407</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>32796000</v>
+        <v>32760454</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>209086500</v>
+        <v>218825860</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>126000000</v>
+        <v>125482639</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1093200000</v>
+        <v>1093031890</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1409958</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>12180564</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1047157</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>9123884</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>704884</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>6093250</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>524182</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>4560550</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>351727</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>3046901</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>264152</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2292276</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>25410000</v>
+        <v>25397900</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>220462000</v>
+        <v>220621319</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11760000</v>
+        <v>11783985</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>102032000</v>
+        <v>101988607</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5355000</v>
+        <v>5336849</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>46461000</v>
+        <v>46464879</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>168525000</v>
+        <v>172303433</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>40561500</v>
+        <v>46522427</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>240000</v>
+        <v>240147</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2160000</v>
+        <v>2161929</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2100000</v>
+        <v>2094726</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>18900000</v>
+        <v>18905582</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1280000</v>
+        <v>1284813</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>11520000</v>
+        <v>11520782</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2340000</v>
+        <v>2334873</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20000000</v>
+        <v>20099754</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>180000000</v>
+        <v>180132332</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2900000</v>
+        <v>2885968</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>26100000</v>
+        <v>26074685</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14200000</v>
+        <v>14259410</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>127800000</v>
+        <v>127940997</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>520000</v>
+        <v>519212</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>4680000</v>
+        <v>4682454</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>20520000</v>
+        <v>20618966</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18180000</v>
+        <v>-18284093</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4700000</v>
+        <v>4676516</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>42300000</v>
+        <v>42265243</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7500000</v>
+        <v>7470975</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>67500000</v>
+        <v>67424251</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7500000</v>
+        <v>7519932</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>67500000</v>
+        <v>67574345</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>240000</v>
+        <v>239720</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2160000</v>
+        <v>2157915</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12440000</v>
+        <v>12387211</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6100000</v>
+        <v>6112268</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>54900000</v>
+        <v>54877182</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6100000</v>
+        <v>6079463</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>54900000</v>
+        <v>54903248</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1000000</v>
+        <v>1004370</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>9000000</v>
+        <v>9002732</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>870000</v>
+        <v>874306</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>7830000</v>
+        <v>7837039</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>125000</v>
+        <v>124442</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1125000</v>
+        <v>1123799</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7225000</v>
+        <v>7241080</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5215000</v>
+        <v>5146131</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>27596500</v>
+        <v>33384465</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>27596500</v>
+        <v>33384465</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
